--- a/stories/arbres/TREE-SEC-063.xlsx
+++ b/stories/arbres/TREE-SEC-063.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Hugo est avec maman, dans le train avec papa. Hugo a envie de jouer. maman est là, tout près. On va apprendre : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo écoute maman. Hugo entend les mots : pieds au sol, protection, adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers la cuisine. Le sol est un peu froid. maman sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Hugo se souvient : pieds au sol, protection, adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. On range un objet. maman dit : je suis là. On reste ensemble.</t>
+          <t>Hugo va vers la cuisine. Le sol est un peu froid. maman sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Hugo se souvient : pieds au sol, protection, adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. On range un objet. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1680,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers la cuisine. Le sol est un peu froid. maman sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Hugo se souvient : pieds au sol, protection, adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. On range un objet.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1870,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Sur le balcon, pieds au sol avec un adulte.</t>
         </is>
       </c>
     </row>
@@ -2009,6 +2047,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo respire. Hugo retient : pieds au sol, protection, adulte. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2195,6 +2238,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2361,6 +2409,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi les cubes. L'eau coule, tout petit bruit. Les cubes reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo répète tout bas : pieds au sol, protection, adulte. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2547,6 +2600,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2713,6 +2771,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de la cuisine, les cubes et le matin. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2875,6 +2938,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3041,6 +3109,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3203,6 +3276,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3369,6 +3447,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et le soir. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3531,6 +3614,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3697,6 +3785,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le livre. Un vélo passe au loin. Le livre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo répète tout bas : pieds au sol, protection, adulte. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3883,6 +3976,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4049,6 +4147,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. Un chat miaule une fois. On range un objet. Cette fin-là est celle de la cuisine, le livre et le matin. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4211,6 +4314,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4377,6 +4485,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la cuisine, le livre et après la sieste. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4539,6 +4652,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4705,6 +4823,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. La couverture est douce. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et le soir. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4867,6 +4990,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5033,6 +5161,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi la dînette. La lumière est claire. La dînette reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo répète tout bas : pieds au sol, protection, adulte. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5219,6 +5352,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5385,6 +5523,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de la cuisine, la dînette et le matin. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5547,6 +5690,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5713,6 +5861,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. La couverture est douce. On dit merci. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5875,6 +6028,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6041,6 +6199,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. On entend un oiseau. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et le soir. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6203,6 +6366,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6227,7 +6395,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers le jardin. Une feuille tombe. maman sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Hugo se souvient : pieds au sol, protection, adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. On dit merci. maman dit : je suis là. On reste ensemble.</t>
+          <t>Hugo va vers le jardin. Une feuille tombe. maman sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Hugo se souvient : pieds au sol, protection, adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6369,6 +6537,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers le jardin. Une feuille tombe. maman sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Hugo se souvient : pieds au sol, protection, adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. On dit merci.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6553,6 +6727,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Sur le balcon, pieds au sol avec un adulte.</t>
         </is>
       </c>
     </row>
@@ -6725,6 +6904,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo respire. Hugo retient : pieds au sol, protection, adulte. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6911,6 +7095,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7077,6 +7266,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi les cubes. Il y a des miettes sur la table. Les cubes reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo répète tout bas : pieds au sol, protection, adulte. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7263,6 +7457,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7429,6 +7628,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le jardin, les cubes et le matin. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7591,6 +7795,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7757,6 +7966,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et après la sieste. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7919,6 +8133,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8085,6 +8304,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et le soir. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8247,6 +8471,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8413,6 +8642,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le livre. Un chat miaule une fois. Le livre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo répète tout bas : pieds au sol, protection, adulte. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8599,6 +8833,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8765,6 +9004,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le jardin, le livre et le matin. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8927,6 +9171,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9093,6 +9342,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. La couverture est douce. On souffle doucement. Cette fin-là est celle de le jardin, le livre et après la sieste. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9255,6 +9509,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9421,6 +9680,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et le soir. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9583,6 +9847,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9749,6 +10018,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi la dînette. Les chaussures font toc toc. La dînette reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo répète tout bas : pieds au sol, protection, adulte. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9935,6 +10209,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10101,6 +10380,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. La couverture est douce. On dit merci. Cette fin-là est celle de le jardin, la dînette et le matin. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10263,6 +10547,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10429,6 +10718,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et après la sieste. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10591,6 +10885,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10757,6 +11056,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et le soir. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10919,6 +11223,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10943,7 +11252,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers la chambre. L'eau coule, tout petit bruit. maman sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Hugo se souvient : pieds au sol, protection, adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. On souffle doucement. maman dit : je suis là. On reste ensemble.</t>
+          <t>Hugo va vers la chambre. L'eau coule, tout petit bruit. maman sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Hugo se souvient : pieds au sol, protection, adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11085,6 +11394,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers la chambre. L'eau coule, tout petit bruit. maman sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Hugo se souvient : pieds au sol, protection, adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. On souffle doucement.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11269,6 +11584,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Sur le balcon, pieds au sol avec un adulte.</t>
         </is>
       </c>
     </row>
@@ -11441,6 +11761,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo respire. Hugo retient : pieds au sol, protection, adulte. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11627,6 +11952,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11793,6 +12123,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi les cubes. La couverture est douce. Les cubes reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo répète tout bas : pieds au sol, protection, adulte. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11979,6 +12314,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12145,6 +12485,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de la chambre, les cubes et le matin. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12307,6 +12652,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12473,6 +12823,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et après la sieste. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12635,6 +12990,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12801,6 +13161,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. On entend un oiseau. On attend son tour. Cette fin-là est celle de la chambre, les cubes et le soir. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12963,6 +13328,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13129,6 +13499,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le livre. On entend un oiseau. Le livre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo répète tout bas : pieds au sol, protection, adulte. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13315,6 +13690,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13481,6 +13861,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. La couverture est douce. On souffle doucement. Cette fin-là est celle de la chambre, le livre et le matin. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13643,6 +14028,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13809,6 +14199,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et après la sieste. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13971,6 +14366,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14137,6 +14537,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de la chambre, le livre et le soir. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14299,6 +14704,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14465,6 +14875,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi la dînette. Ça sent le pain chaud. La dînette reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo répète tout bas : pieds au sol, protection, adulte. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14651,6 +15066,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14817,6 +15237,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. On entend un oiseau. On souffle doucement. Cette fin-là est celle de la chambre, la dînette et le matin. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14979,6 +15404,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15145,6 +15575,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et après la sieste. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15307,6 +15742,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15473,6 +15913,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. Le vent est doux. On attend son tour. Cette fin-là est celle de la chambre, la dînette et le soir. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15635,6 +16080,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15653,7 +16103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15670,6 +16120,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SEC-063.xlsx
+++ b/stories/arbres/TREE-SEC-063.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Hugo est avec maman, dans le train avec papa. Hugo a envie de jouer. maman est là, tout près. On va apprendre : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo écoute maman. Hugo entend les mots : pieds au sol, protection, adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1686,6 +1693,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1877,6 +1885,7 @@
           <t>narrateur|Que fait-on ? Sur le balcon, pieds au sol avec un adulte.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2052,6 +2061,7 @@
           <t>narrateur|Oui. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo respire. Hugo retient : pieds au sol, protection, adulte. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2243,6 +2253,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2414,6 +2425,7 @@
           <t>narrateur|Hugo a choisi les cubes. L'eau coule, tout petit bruit. Les cubes reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo répète tout bas : pieds au sol, protection, adulte. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2605,6 +2617,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2776,6 +2789,7 @@
           <t>narrateur|Hugo rejoint le matin. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de la cuisine, les cubes et le matin. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2943,6 +2957,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3114,6 +3129,7 @@
           <t>narrateur|Hugo rejoint après la sieste. Un chat miaule une fois. On dit merci. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3281,6 +3297,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3452,6 +3469,7 @@
           <t>narrateur|Hugo rejoint le soir. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et le soir. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3619,6 +3637,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3790,6 +3809,7 @@
           <t>narrateur|Hugo a choisi le livre. Un vélo passe au loin. Le livre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo répète tout bas : pieds au sol, protection, adulte. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3981,6 +4001,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4152,6 +4173,7 @@
           <t>narrateur|Hugo rejoint le matin. Un chat miaule une fois. On range un objet. Cette fin-là est celle de la cuisine, le livre et le matin. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4319,6 +4341,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4490,6 +4513,7 @@
           <t>narrateur|Hugo rejoint après la sieste. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de la cuisine, le livre et après la sieste. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4657,6 +4681,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4828,6 +4853,7 @@
           <t>narrateur|Hugo rejoint le soir. La couverture est douce. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et le soir. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4995,6 +5021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5166,6 +5193,7 @@
           <t>narrateur|Hugo a choisi la dînette. La lumière est claire. La dînette reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo répète tout bas : pieds au sol, protection, adulte. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5357,6 +5385,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5528,6 +5557,7 @@
           <t>narrateur|Hugo rejoint le matin. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de la cuisine, la dînette et le matin. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5695,6 +5725,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5866,6 +5897,7 @@
           <t>narrateur|Hugo rejoint après la sieste. La couverture est douce. On dit merci. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6033,6 +6065,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6204,6 +6237,7 @@
           <t>narrateur|Hugo rejoint le soir. On entend un oiseau. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et le soir. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6371,6 +6405,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6543,6 +6578,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6734,6 +6770,7 @@
           <t>narrateur|Que fait-on ? Sur le balcon, pieds au sol avec un adulte.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6909,6 +6946,7 @@
           <t>narrateur|Oui. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo respire. Hugo retient : pieds au sol, protection, adulte. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7100,6 +7138,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7271,6 +7310,7 @@
           <t>narrateur|Hugo a choisi les cubes. Il y a des miettes sur la table. Les cubes reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo répète tout bas : pieds au sol, protection, adulte. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7462,6 +7502,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7633,6 +7674,7 @@
           <t>narrateur|Hugo rejoint le matin. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le jardin, les cubes et le matin. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7800,6 +7842,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7971,6 +8014,7 @@
           <t>narrateur|Hugo rejoint après la sieste. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et après la sieste. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8138,6 +8182,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8309,6 +8354,7 @@
           <t>narrateur|Hugo rejoint le soir. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et le soir. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8476,6 +8522,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8647,6 +8694,7 @@
           <t>narrateur|Hugo a choisi le livre. Un chat miaule une fois. Le livre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo répète tout bas : pieds au sol, protection, adulte. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8838,6 +8886,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9009,6 +9058,7 @@
           <t>narrateur|Hugo rejoint le matin. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le jardin, le livre et le matin. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9176,6 +9226,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9347,6 +9398,7 @@
           <t>narrateur|Hugo rejoint après la sieste. La couverture est douce. On souffle doucement. Cette fin-là est celle de le jardin, le livre et après la sieste. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9514,6 +9566,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9685,6 +9738,7 @@
           <t>narrateur|Hugo rejoint le soir. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et le soir. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9852,6 +9906,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10023,6 +10078,7 @@
           <t>narrateur|Hugo a choisi la dînette. Les chaussures font toc toc. La dînette reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo répète tout bas : pieds au sol, protection, adulte. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10214,6 +10270,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10385,6 +10442,7 @@
           <t>narrateur|Hugo rejoint le matin. La couverture est douce. On dit merci. Cette fin-là est celle de le jardin, la dînette et le matin. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10552,6 +10610,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10723,6 +10782,7 @@
           <t>narrateur|Hugo rejoint après la sieste. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et après la sieste. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10890,6 +10950,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11061,6 +11122,7 @@
           <t>narrateur|Hugo rejoint le soir. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et le soir. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11228,6 +11290,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11400,6 +11463,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11591,6 +11655,7 @@
           <t>narrateur|Que fait-on ? Sur le balcon, pieds au sol avec un adulte.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11766,6 +11831,7 @@
           <t>narrateur|Oui. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo respire. Hugo retient : pieds au sol, protection, adulte. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11957,6 +12023,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12128,6 +12195,7 @@
           <t>narrateur|Hugo a choisi les cubes. La couverture est douce. Les cubes reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo répète tout bas : pieds au sol, protection, adulte. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12319,6 +12387,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12490,6 +12559,7 @@
           <t>narrateur|Hugo rejoint le matin. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de la chambre, les cubes et le matin. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12657,6 +12727,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12828,6 +12899,7 @@
           <t>narrateur|Hugo rejoint après la sieste. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et après la sieste. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12995,6 +13067,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13166,6 +13239,7 @@
           <t>narrateur|Hugo rejoint le soir. On entend un oiseau. On attend son tour. Cette fin-là est celle de la chambre, les cubes et le soir. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13333,6 +13407,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13504,6 +13579,7 @@
           <t>narrateur|Hugo a choisi le livre. On entend un oiseau. Le livre reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo répète tout bas : pieds au sol, protection, adulte. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13695,6 +13771,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13866,6 +13943,7 @@
           <t>narrateur|Hugo rejoint le matin. La couverture est douce. On souffle doucement. Cette fin-là est celle de la chambre, le livre et le matin. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -14033,6 +14111,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14204,6 +14283,7 @@
           <t>narrateur|Hugo rejoint après la sieste. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et après la sieste. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14371,6 +14451,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14542,6 +14623,7 @@
           <t>narrateur|Hugo rejoint le soir. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de la chambre, le livre et le soir. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14709,6 +14791,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14880,6 +14963,7 @@
           <t>narrateur|Hugo a choisi la dînette. Ça sent le pain chaud. La dînette reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo répète tout bas : pieds au sol, protection, adulte. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -15071,6 +15155,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15242,6 +15327,7 @@
           <t>narrateur|Hugo rejoint le matin. On entend un oiseau. On souffle doucement. Cette fin-là est celle de la chambre, la dînette et le matin. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15409,6 +15495,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15580,6 +15667,7 @@
           <t>narrateur|Hugo rejoint après la sieste. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et après la sieste. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15747,6 +15835,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15918,6 +16007,7 @@
           <t>narrateur|Hugo rejoint le soir. Le vent est doux. On attend son tour. Cette fin-là est celle de la chambre, la dînette et le soir. Hugo a appris : Sur le balcon, pieds au sol avec un adulte. Voici le geste : rester derrière la protection ; pieds au sol ; avec un adulte. Hugo a entendu : pieds au sol, protection, adulte. Hugo dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -16085,6 +16175,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16103,7 +16194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16127,6 +16218,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16141,7 +16246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16328,6 +16433,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
